--- a/parsed_reactions_flows.xlsx
+++ b/parsed_reactions_flows.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elber\Documents\git\JSON2SBML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AFEF7B-198D-4722-AFAE-A861E731DE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C597D0A2-A9EE-441F-9712-67E2518AF9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="0" windowWidth="16629" windowHeight="17880" activeTab="1" xr2:uid="{EEC56858-B8A2-471C-8CCB-F4609CE65C47}"/>
+    <workbookView xWindow="-86" yWindow="0" windowWidth="16629" windowHeight="17880" activeTab="4" xr2:uid="{EEC56858-B8A2-471C-8CCB-F4609CE65C47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="CLup" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="central" sheetId="5" r:id="rId3"/>
+    <sheet name="PVS" sheetId="6" r:id="rId4"/>
+    <sheet name="Unused" sheetId="7" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="259">
   <si>
     <t>AB40_monomer_Antibody_bound</t>
   </si>
@@ -660,6 +663,162 @@
   </si>
   <si>
     <t>nM</t>
+  </si>
+  <si>
+    <t>(fta0 * (AB40Mu_central_compartment / AB40Mu_Vcent) * (PK_central_compartment / PK_Vcent) * PK_Vcent)</t>
+  </si>
+  <si>
+    <t>(fta0 * (AB42Mu_central_compartment / AB42Mu_Vcent) * (PK_central_compartment / PK_Vcent) * PK_Vcent)</t>
+  </si>
+  <si>
+    <t>PK_SC_ka * PK_SC_bio * SubCut_absorption_compartment</t>
+  </si>
+  <si>
+    <t>AB42Mu_central_compartment</t>
+  </si>
+  <si>
+    <t>AB42Mu_systemic_synthesis_rate</t>
+  </si>
+  <si>
+    <t>(fta0 * (AB42Mu_central_compartment / AB42Mu_Vcent) * (PK_central_compartment / PK_Vcent) * AB40Mu_Vcent)</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_CSFSAS_Lymph_AB42Mu) * Qbrain_CSF_AB42Mu * AB42Mu_CSF_SAS</t>
+  </si>
+  <si>
+    <t>(AB42Mu_CLd2 * AB42Mu_central_compartment / AB42Mu_Vcent)</t>
+  </si>
+  <si>
+    <t>AB42Mu_CLd2 * AB42Mu_peripheral_compartment / AB42Mu_Vper</t>
+  </si>
+  <si>
+    <t>(AB42Mu_CL / AB42Mu_Vcent * AB42Mu_central_compartment)</t>
+  </si>
+  <si>
+    <t>(Qbrain_plasma - Qlymph_Brain) * AB42Mu_Brain_Plasma</t>
+  </si>
+  <si>
+    <t>(Qbrain_plasma * AB42Mu_central_compartment / AB42Mu_Vcent)</t>
+  </si>
+  <si>
+    <t>(1 - sigma_PVS_ABeta42) * Q_PVS * AB42_Monomer_PVS</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_ISF_lymph_AB42Mu) * Qbrain_ISF_AB42Mu * AB42_Monomer</t>
+  </si>
+  <si>
+    <t>AB40Mb_central_compartment</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_CSFSAS_Lymph) * Qbrain_CSF_AB40Mb * AB40Mb_CSF_SAS</t>
+  </si>
+  <si>
+    <t>(PK_CLd2 * AB40Mb_central_compartment / PK_Vcent)</t>
+  </si>
+  <si>
+    <t>PK_CLd2 * AB40Mb_peripheral_compartment / PK_Vper</t>
+  </si>
+  <si>
+    <t>(PK_CL / PK_Vcent * AB40Mb_central_compartment)</t>
+  </si>
+  <si>
+    <t>(Qbrain_plasma - Qlymph_Brain) * AB40Mb_Brain_Plasma</t>
+  </si>
+  <si>
+    <t>(Qbrain_plasma * AB40Mb_central_compartment / PK_Vcent)</t>
+  </si>
+  <si>
+    <t>fta0 * (AB40Mu_central_compartment / AB40Mu_Vcent) * (PK_central_compartment / PK_Vcent) * PK_Vcent</t>
+  </si>
+  <si>
+    <t>(1 - sigma_PVS_ABeta40_bound) * Q_PVS * AB40_Monomer_PVS_bound</t>
+  </si>
+  <si>
+    <t>(1 - Sigma_ISF_lymph) * Qbrain_ISF_AB40Mb * AB40_monomer_Antibody_bound</t>
+  </si>
+  <si>
+    <t>Qbrain_plasma * (AB40Mu_central_compartment / AB40Mu_Vcent) / Vol_brain_plasma</t>
+  </si>
+  <si>
+    <t>((Qbrain_plasma - Qlymph_Brain) * AB40Mu_Brain_Plasma / Vol_brain_plasma)</t>
+  </si>
+  <si>
+    <t>central is amount</t>
+  </si>
+  <si>
+    <t>peripheral is ?</t>
+  </si>
+  <si>
+    <t>Brain_plasma is concentration</t>
+  </si>
+  <si>
+    <t>((1 - Sigma_v_isf_AB40Mu) * Qbrain_ISF_AB40Mu * AB40Mu_Brain_Plasma / Vol_brain_plasma)</t>
+  </si>
+  <si>
+    <t>Abeta40_plaque_bound_PVS</t>
+  </si>
+  <si>
+    <t>fta3 * C_Antibody_unbound_PVS * Abeta40_plaque_unbound_PVS</t>
+  </si>
+  <si>
+    <t>(CL_Abeta40_plaque_bound_PVS * Abeta40_plaque_bound_PVS)</t>
+  </si>
+  <si>
+    <t>Abeta40_plaque_unbound_PVS</t>
+  </si>
+  <si>
+    <t>(fta3 * C_Antibody_unbound_PVS * Abeta40_plaque_unbound_PVS)</t>
+  </si>
+  <si>
+    <t>(CL_Abeta40_plaque_free_PVS * Abeta40_plaque_unbound_PVS)</t>
+  </si>
+  <si>
+    <t>fta3 * C_Antibody_unbound_PVS * Abeta42_plaque_unbound_PVS</t>
+  </si>
+  <si>
+    <t>Abeta42_plaque_unbound_PVS</t>
+  </si>
+  <si>
+    <t>(fta3 * C_Antibody_unbound_PVS * Abeta42_plaque_unbound_PVS)</t>
+  </si>
+  <si>
+    <t>(CL_abeta42_plaque_free_PVS * Abeta42_plaque_unbound_PVS)</t>
+  </si>
+  <si>
+    <t>Antibody_ISF_to_PVS_bulk_flow: Ab_t =&gt; C_Antibody_unbound_PVS; (1 - sigma_ISF)*Q_PVS*Ab_t;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Antibody_PVS_to_central: C_Antibody_unbound_PVS =&gt; PK_central; (1 - sigma_PVS)*(Q_PVS + CSF_fraction*Qbrain_ISFpsv)*C_Antibody_unbound_PVS;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Antibody_ISF_to_PVS_diffusion: Ab_t =&gt; C_Antibody_unbound_PVS; PS_Ab_ISF_PVS*Ab_t*Pe/(exp(Pe) - 1);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Antibody_PVS_to_ISF_diffusion: C_Antibody_unbound_PVS =&gt; Ab_t; PS_Ab_ISF_PVS*C_Antibody_unbound_PVS*Pe/(exp(Pe) - 1);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AB40_Plaque_bound_clearance: AB40_Plaque_bound_PVS =&gt; $Sink_AB40_Plaque_bound_PVS; CL_AB40_plaque_bound_PVS*AB40_Plaque_bound_PVS;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AB40_Plaque_unbound_clearance: AB40_Plaque_unbound_PVS =&gt; $Sink_AB40_Plaque_unbound_PVS; CL_AB40_plaque_free_PVS*AB40_Plaque_unbound_PVS;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AB42_Plaque_bound_clearance: AB42_Plaque_bound_PVS =&gt; $Sink_AB42_Plaque_bound_PVS; CL_AB42_plaque_bound_PVS*AB42_Plaque_bound_PVS;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AB42_Plaque_unbound_clearance: AB42_Plaque_unbound_PVS =&gt; $Sink_AB42_Plaque_unbound_PVS; CL_AB42_plaque_free_PVS*AB42_Plaque_unbound_PVS;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  subcut_to_central: SubCut_absorption =&gt; PK_central; PK_SC_ka*PK_SC_bio*SubCut_absorption;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  subcut_elimination: SubCut_absorption =&gt; $Sink_SubCut_absorption; PK_SC_ka*(1 - PK_SC_bio)*SubCut_absorption;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  input_to_central: $Source_PK_central =&gt; PK_central; InputCent;</t>
+  </si>
+  <si>
+    <t>input_to_subcut: $Source_SubCut_absorption =&gt; SubCut_absorption; InputSC;</t>
   </si>
 </sst>
 </file>
@@ -689,7 +848,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -714,6 +873,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -727,7 +892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -735,6 +900,7 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4081,6 +4247,614 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F524F3FC-8752-43F0-B3D4-CB184118A007}">
+  <dimension ref="A2:L43"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="27.3046875" customWidth="1"/>
+    <col min="10" max="10" width="21.3046875" customWidth="1"/>
+    <col min="11" max="11" width="3.07421875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" t="s">
+        <v>130</v>
+      </c>
+      <c r="K10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J11" t="s">
+        <v>130</v>
+      </c>
+      <c r="K11" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>210</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>210</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>210</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>210</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J22" t="s">
+        <v>171</v>
+      </c>
+      <c r="K22" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>210</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J23" t="s">
+        <v>171</v>
+      </c>
+      <c r="K23" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>210</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>221</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>221</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>221</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>221</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>221</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>221</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>221</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>221</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>221</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEFAB579-754B-4371-97BF-D67671DF0DCE}">
+  <dimension ref="A2:C9"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="28.765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>246</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15938E98-FD71-432F-BE75-6F13C65DEC96}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1">
+        <v>657</v>
+      </c>
+      <c r="C1">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <f>A1-8</f>
+        <v>649</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>645</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E779CF-3B82-4249-B1B7-FB8EB11A1085}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -4387,7 +5161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E51D95E-FE25-4BAF-8813-72FDE88AAD31}">
   <dimension ref="A2:C41"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
